--- a/web-scraping/atualizar-indicadores/Investimento.xlsx
+++ b/web-scraping/atualizar-indicadores/Investimento.xlsx
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>59.49</v>
+        <v>56.45</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>0.0851</v>
+        <v>0.08439999999999999</v>
       </c>
     </row>
     <row r="4" ht="13.2" customHeight="1">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>58.15</v>
+        <v>55.59</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.1133</v>
+        <v>0.1109</v>
       </c>
     </row>
     <row r="5" ht="13.2" customHeight="1">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>48.57</v>
+        <v>44.51</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>0</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>100.57</v>
+        <v>100.43</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.044</v>
+        <v>0.0429</v>
       </c>
     </row>
     <row r="7" ht="13.2" customHeight="1">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>50.59</v>
+        <v>50.51</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.0445</v>
+        <v>0.0436</v>
       </c>
     </row>
     <row r="8" ht="13.2" customHeight="1">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>9.49</v>
+        <v>9.42</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>10.11</v>
+        <v>10.09</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.1188</v>
+        <v>0.1211</v>
       </c>
     </row>
     <row r="11" ht="13.2" customHeight="1">
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
+        <v>104.01</v>
+      </c>
+      <c r="D11" s="14" t="n">
         <v>102.69</v>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>103.54</v>
-      </c>
       <c r="E11" s="9" t="n">
-        <v>0.09179999999999999</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="12" ht="13.2" customHeight="1">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>126.5</v>
+        <v>129</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>129.27</v>
+        <v>129.14</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.09720000000000001</v>
+        <v>0.0965</v>
       </c>
     </row>
     <row r="13" ht="13.2" customHeight="1">
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>106.24</v>
+        <v>105.08</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>102.27</v>
+        <v>102.29</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.138</v>
+        <v>0.1399</v>
       </c>
     </row>
     <row r="14" ht="13.2" customHeight="1">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>9.789999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>9.390000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.1203</v>
+        <v>0.1224</v>
       </c>
     </row>
     <row r="15" ht="13.2" customHeight="1">
@@ -1007,13 +1007,13 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>93.05</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>101.01</v>
+        <v>100.95</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.1269</v>
+        <v>0.1291</v>
       </c>
     </row>
     <row r="16" ht="13.2" customHeight="1">
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>8.67</v>
+        <v>8.68</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1389</v>
+        <v>0.1371</v>
       </c>
     </row>
     <row r="17" ht="13.2" customHeight="1">
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>110</v>
+        <v>108.64</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>117.99</v>
+        <v>118.07</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.0883</v>
+        <v>0.0901</v>
       </c>
     </row>
     <row r="18" ht="13.2" customHeight="1">
@@ -1055,13 +1055,13 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>102.18</v>
+        <v>100.59</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>105.72</v>
+        <v>106.03</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.0964</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="19" ht="13.2" customHeight="1">
@@ -1071,13 +1071,13 @@
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>111.71</v>
+        <v>109.31</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>110.89</v>
+        <v>109.58</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.0992</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="20" ht="13.2" customHeight="1">
